--- a/forms/trg/Formulir_TRG_womenhealth-con.xlsx
+++ b/forms/trg/Formulir_TRG_womenhealth-con.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B35)</f>
+        <f>COUNTA(Anggota!B5:B36)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F35)</f>
+        <f>COUNTA(Anggota!F5:F36)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,31 +913,43 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Kurniaty, S.E., M.Si.</t>
+          <t>Dr.Andi Nilawati Usman, S.K.M., M.Kes.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Graduate School, Hasanuddin University</t>
+          <t>Midwifery, Graduate School, Hasanuddin University</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Economics, Services Marketing Management</t>
+          <t>Complementary Approach || Epidemiology || Women Health || Biostatistic</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>0009-0009-9515-8831</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>6690560</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>57200071963</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -950,39 +962,31 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr Fendi,S.Si, M.Si</t>
+          <t>Dr. Kurniaty, S.E., M.Si.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Graduate School Laboratory, Hasanuddin University, Indonesia</t>
+          <t>Graduate School, Hasanuddin University</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Material PhysicsIIBiophysicsIIBiomaterial</t>
+          <t>Economics, Services Marketing Management</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-7761-2158</t>
-        </is>
-      </c>
+      <c r="J6" s="12" t="n"/>
       <c r="K6" s="12" t="n"/>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>57200167693</t>
-        </is>
-      </c>
+      <c r="L6" s="12" t="n"/>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -995,31 +999,39 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Mardiana Ahmad, S.Si.T., M. Keb</t>
+          <t>Dr Fendi,S.Si, M.Si</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Graduate School Laboratory, Hasanuddin University, Indonesia</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Midwifery</t>
+          <t>Material PhysicsIIBiophysicsIIBiomaterial</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-7761-2158</t>
+        </is>
+      </c>
       <c r="K7" s="12" t="n"/>
-      <c r="L7" s="12" t="n"/>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>57200167693</t>
+        </is>
+      </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1032,12 +1044,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Jumrah, S.ST., M.Keb.</t>
+          <t>Dr. Mardiana Ahmad, S.Si.T., M. Keb</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1069,12 +1081,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Andi Ariyandy Ph.D MHPE</t>
+          <t>Dr. Jumrah, S.ST., M.Keb.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1084,28 +1096,16 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Endocrine Physiology || Medical and Health Professional</t>
+          <t>Midwifery</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-6492-5235</t>
-        </is>
-      </c>
-      <c r="K9" s="11" t="inlineStr">
-        <is>
-          <t>6688450</t>
-        </is>
-      </c>
-      <c r="L9" s="11" t="inlineStr">
-        <is>
-          <t>59264008500</t>
-        </is>
-      </c>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="12" t="n"/>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Risfah Yulianti,M.Si,Apt.</t>
+          <t>Andi Ariyandy Ph.D MHPE</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Pharmaceutical Chemistry</t>
+          <t>Endocrine Physiology || Medical and Health Professional</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1142,17 +1142,17 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0009-0009-8127-5084</t>
+          <t>0000-0002-6492-5235</t>
         </is>
       </c>
       <c r="K10" s="11" t="inlineStr">
         <is>
-          <t>6016946</t>
+          <t>6688450</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>57195959487</t>
+          <t>59264008500</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1167,22 +1167,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Dr. Burhan Basaran</t>
+          <t>Dr. Risfah Yulianti,M.Si,Apt.</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Recep Tayyip Erdoğan University</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Food and Nutrition||Food engineering||Food Safety||Food and Industry</t>
+          <t>Pharmaceutical Chemistry</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1191,13 +1191,17 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-0080-5047</t>
-        </is>
-      </c>
-      <c r="K11" s="12" t="n"/>
+          <t>0009-0009-8127-5084</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>6016946</t>
+        </is>
+      </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>57188724978</t>
+          <t>57195959487</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1212,22 +1216,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Dr. Khalid ali khan, PhD</t>
+          <t>Dr. Burhan Basaran</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>King Khalid University</t>
+          <t>Recep Tayyip Erdoğan University</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Honeybees || gut bacteria || honey &amp; bee-products analysis || pollination ecology</t>
+          <t>Food and Nutrition||Food engineering||Food Safety||Food and Industry</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1236,13 +1240,13 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-4734-6338</t>
+          <t>0000-0003-0080-5047</t>
         </is>
       </c>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>56709204600</t>
+          <t>57188724978</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1257,31 +1261,39 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Intan Idiana Hassan , BASc, MSc, PhD</t>
+          <t>Dr. Khalid ali khan, PhD</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Universiti Sains Malaysia</t>
+          <t>King Khalid University</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Nursing || Women Health</t>
+          <t>Honeybees || gut bacteria || honey &amp; bee-products analysis || pollination ecology</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n"/>
-      <c r="J13" s="12" t="n"/>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-4734-6338</t>
+        </is>
+      </c>
       <c r="K13" s="12" t="n"/>
-      <c r="L13" s="12" t="n"/>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>56709204600</t>
+        </is>
+      </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1294,22 +1306,22 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Dr. Aminah Dalimunthe, S.Si., M.Si., Apt.</t>
+          <t>Intan Idiana Hassan , BASc, MSc, PhD</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Universitas Sumatera Utara (USU)</t>
+          <t>Universiti Sains Malaysia</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Pharmacology, Pharmacognosy, Natural Product Pharmacy</t>
+          <t>Nursing || Women Health</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1331,22 +1343,22 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Dr. Halisah, S.ST., M.Keb.</t>
+          <t>Dr. Aminah Dalimunthe, S.Si., M.Si., Apt.</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Universitas Sumatera Utara (USU)</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Midwifery</t>
+          <t>Pharmacology, Pharmacognosy, Natural Product Pharmacy</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1354,11 +1366,7 @@
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="12" t="n"/>
       <c r="J15" s="12" t="n"/>
-      <c r="K15" s="11" t="inlineStr">
-        <is>
-          <t>6786487</t>
-        </is>
-      </c>
+      <c r="K15" s="12" t="n"/>
       <c r="L15" s="12" t="n"/>
       <c r="M15" s="11" t="inlineStr">
         <is>
@@ -1372,12 +1380,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Dinah Inrawati Agustin, S.Tr.Keb.,M.keb</t>
+          <t>Dr. Halisah, S.ST., M.Keb.</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1394,17 +1402,13 @@
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
       <c r="I16" s="12" t="n"/>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-6192-5953</t>
-        </is>
-      </c>
-      <c r="K16" s="12" t="n"/>
-      <c r="L16" s="11" t="inlineStr">
-        <is>
-          <t>58996821600</t>
-        </is>
-      </c>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="11" t="inlineStr">
+        <is>
+          <t>6786487</t>
+        </is>
+      </c>
+      <c r="L16" s="12" t="n"/>
       <c r="M16" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1417,12 +1421,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Zafitri Nulandari, S.Tr.Keb., Bdn.,M.Keb</t>
+          <t>Dinah Inrawati Agustin, S.Tr.Keb.,M.keb</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1441,13 +1445,13 @@
       <c r="I17" s="12" t="n"/>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-7745-9501</t>
+          <t>0000-0001-6192-5953</t>
         </is>
       </c>
       <c r="K17" s="12" t="n"/>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>58996821500</t>
+          <t>58996821600</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
@@ -1462,12 +1466,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Andi Husnul Khatimah</t>
+          <t>Zafitri Nulandari, S.Tr.Keb., Bdn.,M.Keb</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1484,9 +1488,17 @@
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
       <c r="I18" s="12" t="n"/>
-      <c r="J18" s="12" t="n"/>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-7745-9501</t>
+        </is>
+      </c>
       <c r="K18" s="12" t="n"/>
-      <c r="L18" s="12" t="n"/>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>58996821500</t>
+        </is>
+      </c>
       <c r="M18" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1499,12 +1511,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Suryana</t>
+          <t>Andi Husnul Khatimah</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1536,12 +1548,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Suci Rahma Dani</t>
+          <t>Suryana</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1573,12 +1585,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Ayu Lestari has</t>
+          <t>Suci Rahma Dani</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1610,12 +1622,12 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Riska Purnamasari</t>
+          <t>Ayu Lestari has</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1647,12 +1659,12 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Siti Alopasaribu</t>
+          <t>Riska Purnamasari</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -1682,10 +1694,26 @@
       <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="11" t="n"/>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Siti Alopasaribu</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>Midwifery</t>
+        </is>
+      </c>
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="12" t="n"/>
       <c r="H24" s="12" t="n"/>
@@ -1693,7 +1721,11 @@
       <c r="J24" s="12" t="n"/>
       <c r="K24" s="12" t="n"/>
       <c r="L24" s="12" t="n"/>
-      <c r="M24" s="12" t="n"/>
+      <c r="M24" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1882,15 +1914,32 @@
       <c r="L35" s="12" t="n"/>
       <c r="M35" s="12" t="n"/>
     </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="12" t="n"/>
+      <c r="C36" s="12" t="n"/>
+      <c r="D36" s="12" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="12" t="n"/>
+      <c r="G36" s="12" t="n"/>
+      <c r="H36" s="12" t="n"/>
+      <c r="I36" s="12" t="n"/>
+      <c r="J36" s="12" t="n"/>
+      <c r="K36" s="12" t="n"/>
+      <c r="L36" s="12" t="n"/>
+      <c r="M36" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
